--- a/stories/arbres/TREE-LAN-001.xlsx
+++ b/stories/arbres/TREE-LAN-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maya est au bord de la mer, avec maman. Dans le sac, une pomme, une poire, un chapeau, une chaussette. Maman dit : on nomme. On classe. Une catégorie. Les fruits ensemble. Les habits ensemble. Maya pose pomme et poire. Catégorie fruits. Puis le chapeau. Catégorie habits. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+          <t>Maya est au bord de la mer, avec maman. Dans le sac, une pomme, une poire, un chapeau, une chaussette. On nomme. On classe. Une catégorie. Les fruits ensemble. Les habits ensemble. Maya pose pomme et poire. Catégorie fruits. Puis le chapeau. Catégorie habits. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maya est au bord de la mer, avec maman. Dans le sac, une pomme, une poire, un chapeau, une chaussette.
+maman|On nomme. On classe.
+narrateur|Une catégorie. Les fruits ensemble. Les habits ensemble. Maya pose pomme et poire. Catégorie fruits. Puis le chapeau. Catégorie habits. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1540,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Maya pose le ballon rouge avec.. Non. Le ballon n'est pas un fruit. Maman dit : catégorie. Fruits ici. Habits là. Maya classe. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+          <t>Maya pose le ballon rouge avec.. Non. Le ballon n'est pas un fruit. Catégorie. Fruits ici. Habits là. Maya classe. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1678,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose le ballon rouge avec.. Non. Le ballon n'est pas un fruit.
+maman|Catégorie. Fruits ici. Habits là.
+narrateur|Maya classe. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Pomme et poire. C'est quelle catégorie ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a classé. Catégorie fruits. Catégorie habits. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2185,6 +2231,11 @@
       <c r="AV7" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2349,6 +2400,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Tom. Un rire court, tout petit. Tom donne une banane. Catégorie fruits. Maya met ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2591,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2758,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La lumière est claire. On souffle doucement. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2925,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3092,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On écoute jusqu'au bout. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3259,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3426,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un chat miaule une fois. On attend son tour. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Léa. Le papier froisse, chut. Léa donne une écharpe. Catégorie habits. Ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3951,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3980,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Les chaussures font toc toc. On sourit ensemble. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Les chaussures font toc toc. On sourit ensemble. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4118,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Les chaussures font toc toc. On sourit ensemble. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La couverture est douce. On pose les pieds par terre. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. On souffle. Maya sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4665,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Une cloche tinte au loin. On parle tout bas. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Sami. Une goutte tombe, ploc. Sami donne une orange. Catégorie fruits. Maya classe. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5312,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5479,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le bois sent le chaud. On range les jouets. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5646,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5813,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On s'assoit un moment. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5980,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6147,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon sent la fleur. On respire, un, deux. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6314,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6309,6 +6481,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose le seau. Dedans, une chaussette. Catégorie habits. Une pomme à côté. Catégorie fruits. On met ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6666,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Chapeau et chaussette. Quelle catégorie ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6839,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Ensemble. Une catégorie. Maman sourit. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6845,6 +7032,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7009,6 +7201,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Tom. Un ruisseau chante. Tom pose un gant. Habits. Catégorie. Maya met ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7392,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7421,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Le tissu est tout doux. On referme le sac. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Le tissu est tout doux. On referme le sac. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7559,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Le tissu est tout doux. On referme le sac. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7727,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7681,6 +7894,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Une cuillère tinte. On essuie une miette. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. On souffle. Maya sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8061,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8005,6 +8228,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le sable est tiède. On met le doudou près. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8395,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8562,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Léa. Le coussin est moelleux. Léa dit poire. Fruits. Catégorie. Ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8515,6 +8753,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8677,6 +8920,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un rire court, tout petit. On lace les chaussures. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8839,6 +9087,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9001,6 +9254,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On met le manteau. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9163,6 +9421,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9325,6 +9588,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On boit une gorgée. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9487,6 +9755,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9649,6 +9922,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Sami. La terre est un peu humide. Sami range. Une catégorie. Habits ici. Fruits là. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9835,6 +10113,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9859,7 +10142,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. Un pigeon roucoule. On feuillette le livre. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. Un pigeon roucoule. On feuillette le livre. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9997,6 +10280,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Un pigeon roucoule. On feuillette le livre. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10159,6 +10448,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10321,6 +10615,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On referme le livre. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. On souffle. Maya sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10483,6 +10782,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10645,6 +10949,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On pose le ballon. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10807,6 +11116,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10831,7 +11145,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Maya pose le doudou. Maman dit : le doudou n'est pas un fruit. Catégorie. Maya remet la poire avec la pomme. Ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+          <t>Maya pose le doudou. Le doudou n'est pas un fruit. Catégorie. Maya remet la poire avec la pomme. Ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10969,6 +11283,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Maya pose le doudou.
+maman|Le doudou n'est pas un fruit. Catégorie.
+narrateur|Maya remet la poire avec la pomme. Ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11145,6 +11466,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On met ensemble. On fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -11313,6 +11639,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Maya a nommé. Maya a mis ensemble. Catégorie. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11501,6 +11832,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11665,6 +12001,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Tom. La laine gratte un peu. Tom écoute. Maya nomme. Catégorie. On met ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11851,6 +12192,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12013,6 +12359,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La corde du sac est rêche. On secoue le sable. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12175,6 +12526,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12337,6 +12693,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On caresse le tissu. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12499,6 +12860,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12661,6 +13027,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un ruisseau chante. On tend la main. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12823,6 +13194,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12985,6 +13361,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Léa. Une pomme sent le sucré. Léa sourit. Maya classe encore. Catégorie. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13171,6 +13552,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13195,7 +13581,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Voilà le matin. La laine gratte un peu. On chante un petit air. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range. Maman dit : c'est bien.</t>
+          <t>Voilà le matin. La laine gratte un peu. On chante un petit air. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13333,6 +13719,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. La laine gratte un peu. On chante un petit air. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13495,6 +13887,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13657,6 +14054,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Un pain croustille. On compte jusqu'à trois. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. On souffle. Maya sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13819,6 +14221,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13981,6 +14388,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Le savon glisse. On montre du doigt. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14143,6 +14555,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14305,6 +14722,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Maya va vers Sami. Un rire court, tout petit. Sami applaudit. Ensemble. Catégorie fruits. Catégorie habits. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14491,6 +14913,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14653,6 +15080,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le matin. Une plume vole. On range la chaise. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14815,6 +15247,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14977,6 +15414,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà après la sieste. Le banc est lisse. On range un objet. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15139,6 +15581,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15301,6 +15748,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Voilà le soir. Un grelot sonne. On se tient la main. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15463,6 +15915,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15481,7 +15938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15512,6 +15969,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-LAN-001.xlsx
+++ b/stories/arbres/TREE-LAN-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Une catégorie. Les fruits ensemble. Les habits ensemble. Maya pose pomme et poire. Catégorie fruits. Puis le chapeau. Catégorie habits. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
 narrateur|Maya classe. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|Pomme et poire. C'est quelle catégorie ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Maya a classé. Catégorie fruits. Catégorie habits. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2238,6 +2248,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2405,6 +2416,7 @@
           <t>narrateur|Maya va vers Tom. Un rire court, tout petit. Tom donne une banane. Catégorie fruits. Maya met ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2596,6 +2608,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2763,6 +2776,7 @@
           <t>narrateur|Voilà le matin. La lumière est claire. On souffle doucement. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2930,6 +2944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3112,7 @@
           <t>narrateur|Voilà après la sieste. Des miettes dorment sur la table. On écoute jusqu'au bout. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3448,7 @@
           <t>narrateur|Voilà le soir. Un chat miaule une fois. On attend son tour. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3784,7 @@
           <t>narrateur|Maya va vers Léa. Le papier froisse, chut. Léa donne une écharpe. Catégorie habits. Ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3956,6 +3976,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Voilà après la sieste. La couverture est douce. On pose les pieds par terre. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. On souffle. Maya sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Voilà le soir. Une cloche tinte au loin. On parle tout bas. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Maya va vers Sami. Une goutte tombe, ploc. Sami donne une orange. Catégorie fruits. Maya classe. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5317,6 +5345,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5484,6 +5513,7 @@
           <t>narrateur|Voilà le matin. Le bois sent le chaud. On range les jouets. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5651,6 +5681,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5818,6 +5849,7 @@
           <t>narrateur|Voilà après la sieste. Une goutte tombe, ploc. On s'assoit un moment. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5985,6 +6017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6152,6 +6185,7 @@
           <t>narrateur|Voilà le soir. Le savon sent la fleur. On respire, un, deux. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6319,6 +6353,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6486,6 +6521,7 @@
           <t>narrateur|Maya pose le seau. Dedans, une chaussette. Catégorie habits. Une pomme à côté. Catégorie fruits. On met ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6673,6 +6709,7 @@
           <t>narrateur|Chapeau et chaussette. Quelle catégorie ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6844,6 +6881,7 @@
           <t>narrateur|Ensemble. Une catégorie. Maman sourit. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7039,6 +7077,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7206,6 +7245,7 @@
           <t>narrateur|Maya va vers Tom. Un ruisseau chante. Tom pose un gant. Habits. Catégorie. Maya met ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7397,6 +7437,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7565,6 +7606,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7732,6 +7774,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7899,6 +7942,7 @@
           <t>narrateur|Voilà après la sieste. Une cuillère tinte. On essuie une miette. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. On souffle. Maya sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8066,6 +8110,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8233,6 +8278,7 @@
           <t>narrateur|Voilà le soir. Le sable est tiède. On met le doudou près. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8400,6 +8446,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8567,6 +8614,7 @@
           <t>narrateur|Maya va vers Léa. Le coussin est moelleux. Léa dit poire. Fruits. Catégorie. Ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8758,6 +8806,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8925,6 +8974,7 @@
           <t>narrateur|Voilà le matin. Un rire court, tout petit. On lace les chaussures. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9092,6 +9142,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9259,6 +9310,7 @@
           <t>narrateur|Voilà après la sieste. Le papier froisse, chut. On met le manteau. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9426,6 +9478,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9593,6 +9646,7 @@
           <t>narrateur|Voilà le soir. L'herbe chatouille le mollet. On boit une gorgée. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9760,6 +9814,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9927,6 +9982,7 @@
           <t>narrateur|Maya va vers Sami. La terre est un peu humide. Sami range. Une catégorie. Habits ici. Fruits là. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10118,6 +10174,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10286,6 +10343,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10453,6 +10511,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10620,6 +10679,7 @@
           <t>narrateur|Voilà après la sieste. La fenêtre vibre un peu. On referme le livre. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. On souffle. Maya sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10787,6 +10847,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10954,6 +11015,7 @@
           <t>narrateur|Voilà le soir. Le lait est froid dans le verre. On pose le ballon. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11121,6 +11183,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11290,6 +11353,7 @@
 narrateur|Maya remet la poire avec la pomme. Ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11473,6 +11537,7 @@
           <t>narrateur|On met ensemble. On fait quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11644,6 +11709,7 @@
           <t>narrateur|Maya a nommé. Maya a mis ensemble. Catégorie. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11839,6 +11905,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12006,6 +12073,7 @@
           <t>narrateur|Maya va vers Tom. La laine gratte un peu. Tom écoute. Maya nomme. Catégorie. On met ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12197,6 +12265,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12364,6 +12433,7 @@
           <t>narrateur|Voilà le matin. La corde du sac est rêche. On secoue le sable. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12531,6 +12601,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12698,6 +12769,7 @@
           <t>narrateur|Voilà après la sieste. Le savon mousse entre les doigts. On caresse le tissu. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12865,6 +12937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13032,6 +13105,7 @@
           <t>narrateur|Voilà le soir. Un ruisseau chante. On tend la main. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13199,6 +13273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13366,6 +13441,7 @@
           <t>narrateur|Maya va vers Léa. Une pomme sent le sucré. Léa sourit. Maya classe encore. Catégorie. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13557,6 +13633,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13725,6 +13802,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13892,6 +13970,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14059,6 +14138,7 @@
           <t>narrateur|Voilà après la sieste. Un pain croustille. On compte jusqu'à trois. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. On souffle. Maya sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14226,6 +14306,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14393,6 +14474,7 @@
           <t>narrateur|Voilà le soir. Le savon glisse. On montre du doigt. On a nommé. On a classé. Une catégorie. La mer chante. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14560,6 +14642,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14727,6 +14810,7 @@
           <t>narrateur|Maya va vers Sami. Un rire court, tout petit. Sami applaudit. Ensemble. Catégorie fruits. Catégorie habits. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14918,6 +15002,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15085,6 +15170,7 @@
           <t>narrateur|Voilà le matin. Une plume vole. On range la chaise. On a nommé. On a classé. Une catégorie. Les fruits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maya dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15252,6 +15338,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15419,6 +15506,7 @@
           <t>narrateur|Voilà après la sieste. Le banc est lisse. On range un objet. On a nommé. On a classé. Une catégorie. Les habits sont ensemble. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Maman serre Maya tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15586,6 +15674,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15753,6 +15842,7 @@
           <t>narrateur|Voilà le soir. Un grelot sonne. On se tient la main. On a nommé. On a classé. Une catégorie. Le sac est plus clair. On met ensemble. C'est une catégorie. Fruits avec fruits. Habits avec habits. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15920,6 +16010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15938,7 +16029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15976,6 +16067,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15990,7 +16095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16177,6 +16282,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
